--- a/260623.xlsx
+++ b/260623.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tac3\new\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2571947C-AFCD-476B-AF8C-ADBB87338272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C20909-84A8-4648-9BA9-C1863EE3BFB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8890" yWindow="2290" windowWidth="16180" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9260" yWindow="4110" windowWidth="16150" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>unter Generalverdacht zu stellen, da bin ich sehr froh darüber, dass auch der CDU-Bundesinnenminister das nicht mitmachen will.
 Diese scharfmacherischen Vorschläge aus den Reihen der CDU und der CSU gehen ja eher ein bisschen zurück in die unseligen Zeiten, in denen ein CDU-Ministerpräsident in Hessen, Herr Koch, einen ausländerfeindlichen Wahlkampf gemacht hat.
@@ -617,17 +617,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Anzahl, dahinterstehende Lieferanten.
-Und die wechselseitige Beziehung – Sie sprachen es an mit den Motorenlieferungen
-Was bedeutet das denn für die Ford Investitionspolitik am Standort Europa?
-Werden geplante Investitionen gestoppt?
-Mattes: Nein, überhaupt nicht.
-Wir haben derzeit überhaupt keinerlei Veranlassung, unsere Pläne zu ändern.
-und denen will ich überhaupt nicht vorgreifen.
-Denn wir haben ja noch überhaupt keine Veränderung der Rahmenbedingungen, die dazu Anlass bieten.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Remme: Die Kanzlerin sagt: Wieso fragen alle nach unserem Plan?
 Sollen die Briten doch erst mal einen vorlegen.
 Hat sie recht?
@@ -699,6 +688,12 @@
 Das würde ja innerhalb Europas andere anregen, dem Beispiel gar noch folgen zu wollen.
 muss es alle Freizügigkeiten auch gewähren, die im Binnenmarkt garantiert sind.</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>am Standort</t>
+  </si>
+  <si>
+    <t>Anlass bieten</t>
   </si>
 </sst>
 </file>
@@ -1039,15 +1034,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="280" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1066,7 +1066,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="322" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="2" spans="1:5" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
